--- a/results/Int All Data -0.7/Rando_7_permute.xlsx
+++ b/results/Int All Data -0.7/Rando_7_permute.xlsx
@@ -440,1523 +440,1523 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8992104527669089</v>
+        <v>0.8866472131955169</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8992104527669089</v>
+        <v>0.8934148736945489</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9005492605470342</v>
+        <v>0.9101731627364971</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8985042380776433</v>
+        <v>0.9101731627364971</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8964592156082525</v>
+        <v>0.9119386994596609</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8944878147372676</v>
+        <v>0.9132925078871825</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8941647086874276</v>
+        <v>0.9107921368185363</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.891605716667772</v>
+        <v>0.911218865761575</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9098200553918643</v>
+        <v>0.9107771361711401</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9082167625129085</v>
+        <v>0.9107771361711401</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9070251979295949</v>
+        <v>0.9144990731178925</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9083053847587106</v>
+        <v>0.9083790063571164</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9083053847587106</v>
+        <v>0.9085412502013245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9063339838877257</v>
+        <v>0.9088643562511645</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9066870912323584</v>
+        <v>0.8902655272490707</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9052746618538274</v>
+        <v>0.8953998935743542</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9033618819338519</v>
+        <v>0.8947522998360982</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9037886108768904</v>
+        <v>0.8947522998360982</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9061717400435176</v>
+        <v>0.8958116218699965</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8834692470938219</v>
+        <v>0.8970031864533101</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8834692470938219</v>
+        <v>0.8874556691394049</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8859409985062513</v>
+        <v>0.8779953924327261</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8859409985062513</v>
+        <v>0.8807466295913824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8888394788617193</v>
+        <v>0.8806730079929765</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8930767669973125</v>
+        <v>0.8782012565805472</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8934298743419453</v>
+        <v>0.8867494544501394</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8934298743419453</v>
+        <v>0.8864399674091197</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8800117952459001</v>
+        <v>0.8500085266837831</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8825571682567352</v>
+        <v>0.8548784079102361</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.882910275601368</v>
+        <v>0.8495817977407446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8870889427859519</v>
+        <v>0.842872758192722</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8916207173151683</v>
+        <v>0.8455803750477652</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8962111127953943</v>
+        <v>0.8484202344522238</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8933862540383322</v>
+        <v>0.8476267791557319</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8875306723763867</v>
+        <v>0.8476267791557319</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8907522587816947</v>
+        <v>0.8457876208341624</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8951517907614961</v>
+        <v>0.8473322927621088</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8948723050152692</v>
+        <v>0.851333715455088</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.891120366773724</v>
+        <v>0.8424760305444761</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8865463535794703</v>
+        <v>0.8485088566980259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8866049745304798</v>
+        <v>0.8394016873359798</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8866785961288856</v>
+        <v>0.8395775501890081</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8518668305684771</v>
+        <v>0.8262330926913688</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8656816373127683</v>
+        <v>0.8085777254597304</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8633135087935374</v>
+        <v>0.8057964870062813</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8633135087935374</v>
+        <v>0.8010002273782342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8559568755072587</v>
+        <v>0.8039273273899189</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8442048551569068</v>
+        <v>0.8022940332161703</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8081973800974569</v>
+        <v>0.8019409258715375</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.803327498871004</v>
+        <v>0.8016614401253106</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8084482461874671</v>
+        <v>0.8008079822392336</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8057706306272165</v>
+        <v>0.7990274448686733</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7994460813571954</v>
+        <v>0.7892726817683711</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7874118119834645</v>
+        <v>0.7836229642542467</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7823196843232181</v>
+        <v>0.7703957486586264</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7824669275200298</v>
+        <v>0.7488411999886311</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7827886519312939</v>
+        <v>0.7605673639599182</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7722104322397072</v>
+        <v>0.7532107306736396</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7879530195513701</v>
+        <v>0.7542550520601415</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.788232505297597</v>
+        <v>0.7499591429735388</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.798340375742532</v>
+        <v>0.7191501817446858</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7986934830871648</v>
+        <v>0.7155454866999523</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7980608899963051</v>
+        <v>0.6669189143952529</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7948093022962044</v>
+        <v>0.6636823273425485</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.789439070528307</v>
+        <v>0.6614900616763461</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8056083867830085</v>
+        <v>0.6439669369941229</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7711361095584125</v>
+        <v>0.6493807890656333</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7607787546620433</v>
+        <v>0.6290914265773575</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7640589620183609</v>
+        <v>0.6331228505651296</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7621025617947722</v>
+        <v>0.6331228505651296</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7631618838286705</v>
+        <v>0.6284588334864978</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7698123024256837</v>
+        <v>0.5400633737877109</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7698859240240894</v>
+        <v>0.5400633737877109</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7570854373715076</v>
+        <v>0.5393571590984453</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7531726369243303</v>
+        <v>0.5380769722693295</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7430347651846028</v>
+        <v>0.5380769722693295</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7399290390427375</v>
+        <v>0.5250856221163229</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7338089722819616</v>
+        <v>0.5257182152071826</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7352214016604928</v>
+        <v>0.5256445936087768</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7270413117829295</v>
+        <v>0.5341191698799632</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7294394415969532</v>
+        <v>0.5329862262476591</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7321320578046</v>
+        <v>0.5329862262476591</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7605865095230426</v>
+        <v>0.5256445936087768</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7605865095230426</v>
+        <v>0.5238054352872071</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7557902498949955</v>
+        <v>0.5238054352872071</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7561433572396282</v>
+        <v>0.5238054352872071</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7476687809684418</v>
+        <v>0.5107404635357947</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7471684304269974</v>
+        <v>0.5140656728343013</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7498024256836349</v>
+        <v>0.5091221700094425</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7434070180923598</v>
+        <v>0.5079156047787325</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7415828604181864</v>
+        <v>0.5081950905249595</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7423626967058579</v>
+        <v>0.5052966101694916</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7457915288975629</v>
+        <v>0.5120056497175142</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7380231673156421</v>
+        <v>0.5123587570621468</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7409516489659027</v>
+        <v>0.5098870056497176</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7381267902088406</v>
+        <v>0.5098870056497176</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7249323391851649</v>
+        <v>0.5098870056497176</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7255240752495634</v>
+        <v>0.5081214689265536</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7241307914341566</v>
+        <v>0.5081214689265536</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7249270100078004</v>
+        <v>0.509180790960452</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7240135495321377</v>
+        <v>0.509180790960452</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6136557604065018</v>
+        <v>0.509180790960452</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6128173031678209</v>
+        <v>0.513771186440678</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6244412258844856</v>
+        <v>0.513771186440678</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6286307488007377</v>
+        <v>0.5092694132062542</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6366049745304797</v>
+        <v>0.5080042270245347</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5852530214461887</v>
+        <v>0.5029871026012701</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5837969717640445</v>
+        <v>0.5029871026012701</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5788398499303654</v>
+        <v>0.5031343457980818</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5823709233766931</v>
+        <v>0.5005889727872466</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5610672407967081</v>
+        <v>0.5005889727872466</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5625832930684377</v>
+        <v>0.5010593220338984</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5625832930684377</v>
+        <v>0.4991615427613192</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5629500194218908</v>
+        <v>0.5000736215984058</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5677776619833066</v>
+        <v>0.5000736215984058</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5648191790382532</v>
+        <v>0.5000736215984058</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5332234733288489</v>
+        <v>0.499514650105952</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.538460080908755</v>
+        <v>0.499514650105952</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5479503589102267</v>
+        <v>0.499514650105952</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5240263000824247</v>
+        <v>0.5003531073446328</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5233200853931591</v>
+        <v>0.499514650105952</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5244380283780669</v>
+        <v>0.4989556786134981</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5177289888300443</v>
+        <v>0.4994410285075461</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5202021218810496</v>
+        <v>0.4997205142537731</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5202021218810496</v>
+        <v>0.4997205142537731</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5196431503885958</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5088290652543952</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5098583859935008</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5050171244232646</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5040314239877721</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5040314239877721</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5040314239877721</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5043845313324049</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5045767764714056</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5036060766833095</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5044895358641794</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4979863604639779</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5008398388772568</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4993537879003199</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4993537879003199</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4993537879003199</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4998391377943679</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4995746526955374</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4995746526955374</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5013251887713048</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5011329436323041</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5004267289430386</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5004267289430386</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5004267289430386</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5004267289430386</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5004267289430386</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B156" t="n">
